--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/FLORIDA_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/FLORIDA_2021.xlsx
@@ -3408,7 +3408,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C170">
@@ -5575,7 +5575,7 @@
         <v>27</v>
       </c>
       <c r="D290">
-        <v>0.0009931217125832199</v>
+        <v>0.0009931217125832201</v>
       </c>
     </row>
     <row r="291">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C340">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C350">
@@ -6997,7 +6997,7 @@
         <v>27</v>
       </c>
       <c r="D369">
-        <v>0.0009931217125832199</v>
+        <v>0.0009931217125832201</v>
       </c>
     </row>
     <row r="370">
@@ -7879,7 +7879,7 @@
         <v>27</v>
       </c>
       <c r="D418">
-        <v>0.0009931217125832199</v>
+        <v>0.0009931217125832201</v>
       </c>
     </row>
     <row r="419">
@@ -9553,7 +9553,7 @@
         <v>27</v>
       </c>
       <c r="D511">
-        <v>0.0009931217125832199</v>
+        <v>0.0009931217125832201</v>
       </c>
     </row>
     <row r="512">
@@ -12451,7 +12451,7 @@
         <v>27</v>
       </c>
       <c r="D672">
-        <v>0.0009931217125832199</v>
+        <v>0.0009931217125832201</v>
       </c>
     </row>
     <row r="673">
@@ -13801,7 +13801,7 @@
         <v>27</v>
       </c>
       <c r="D747">
-        <v>0.0009931217125832199</v>
+        <v>0.0009931217125832201</v>
       </c>
     </row>
     <row r="748">
@@ -14568,7 +14568,7 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C790">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>San Bartolome Yucane</t>
+          <t>San Bartolome Yucuane</t>
         </is>
       </c>
       <c r="C883">
@@ -17268,7 +17268,7 @@
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C940">
@@ -17286,7 +17286,7 @@
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C941">
@@ -18330,7 +18330,7 @@
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C999">
@@ -18348,7 +18348,7 @@
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1000">
@@ -20436,7 +20436,7 @@
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C1116">
@@ -27949,7 +27949,7 @@
         <v>27</v>
       </c>
       <c r="D1533">
-        <v>0.0009931217125832199</v>
+        <v>0.0009931217125832201</v>
       </c>
     </row>
     <row r="1534">
@@ -29065,7 +29065,7 @@
         <v>27</v>
       </c>
       <c r="D1595">
-        <v>0.0009931217125832199</v>
+        <v>0.0009931217125832201</v>
       </c>
     </row>
     <row r="1596">
